--- a/artfynd/A 59990-2025 artfynd.xlsx
+++ b/artfynd/A 59990-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130156819</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130156828</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59990-2025 artfynd.xlsx
+++ b/artfynd/A 59990-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130156819</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130156828</v>
       </c>
       <c r="B3" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59990-2025 artfynd.xlsx
+++ b/artfynd/A 59990-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,103 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130692775</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lommeberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>420239</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6372028</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Öreryd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Karin Ramnemo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Karin Ramnemo</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59990-2025 artfynd.xlsx
+++ b/artfynd/A 59990-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156819</v>
+        <v>130692775</v>
       </c>
       <c r="B2" t="n">
-        <v>58011</v>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +775,7 @@
         <v>130156828</v>
       </c>
       <c r="B3" t="n">
-        <v>58224</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130692775</v>
+        <v>130156819</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59990-2025 artfynd.xlsx
+++ b/artfynd/A 59990-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130692775</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130156828</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130156819</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>